--- a/results/Int Task Remove ACC -0.8/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_6_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6121912188425346</v>
+        <v>0.6203494265350264</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6120319895283779</v>
+        <v>0.62106575891325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6120319895283779</v>
+        <v>0.6218617059485517</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6104798030185727</v>
+        <v>0.6218615064130704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6066582994788133</v>
+        <v>0.6149773327693131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6214642312696044</v>
+        <v>0.6315323925900505</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6225387298369396</v>
+        <v>0.6300598207373236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6278318075520188</v>
+        <v>0.6308156611408641</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6328862408313447</v>
+        <v>0.626955846788676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6296230375685404</v>
+        <v>0.6217425832661564</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6293051775466714</v>
+        <v>0.6195540781061688</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6398516254160315</v>
+        <v>0.6192364176197812</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6367077443711041</v>
+        <v>0.6237329496931144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6420800376722989</v>
+        <v>0.6233350759432043</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6432740579929923</v>
+        <v>0.626955846788676</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6420403301115004</v>
+        <v>0.639253218507315</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6432339513612311</v>
+        <v>0.639253218507315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6405280506979751</v>
+        <v>0.6381787199399798</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.638021485980637</v>
+        <v>0.6393725407251918</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.638021485980637</v>
+        <v>0.6443072527156779</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6427963700505224</v>
+        <v>0.6522266164369348</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6601481750484871</v>
+        <v>0.6361498431651116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6548550973334077</v>
+        <v>0.6289079024032054</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6519111508408425</v>
+        <v>0.6168507714041711</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6592329057953086</v>
+        <v>0.6213479020839485</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6556911510004708</v>
+        <v>0.6234571916578207</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.657083908660638</v>
+        <v>0.6261632918565579</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6156994516764971</v>
+        <v>0.6295458173372389</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6084573113791094</v>
+        <v>0.6284709196989409</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6100492054497131</v>
+        <v>0.6287494712309742</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.603043714233265</v>
+        <v>0.6356735519710115</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6090930314228477</v>
+        <v>0.6451047960348308</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6098490713618696</v>
+        <v>0.6314968752743613</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5817145684845679</v>
+        <v>0.6455437740939094</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5901904366634475</v>
+        <v>0.6233791732845935</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.595960803250034</v>
+        <v>0.6233791732845935</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6046749167937042</v>
+        <v>0.6215087276819564</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6088531897742057</v>
+        <v>0.6313382445666489</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5997394066612924</v>
+        <v>0.6129959454390179</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6063456273794606</v>
+        <v>0.6250538745799779</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6079373219145829</v>
+        <v>0.5952883686777183</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5526266850771404</v>
+        <v>0.5793317157656974</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4983115307563991</v>
+        <v>0.5793317157656974</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5102511353568892</v>
+        <v>0.5864136290715215</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5167775418824976</v>
+        <v>0.5904723802986647</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.515662936683401</v>
+        <v>0.5732007885642225</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5268457032029435</v>
+        <v>0.5732007885642225</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5401359634770255</v>
+        <v>0.5739957379221172</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5401359634770255</v>
+        <v>0.5544997246410357</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5421656383938191</v>
+        <v>0.5641311027926985</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5449112466178736</v>
+        <v>0.568349881475924</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5152642647915653</v>
+        <v>0.5372694367512432</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5162591487018222</v>
+        <v>0.517657293819987</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5217509637563752</v>
+        <v>0.5547864571278065</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5299492780806283</v>
+        <v>0.5574119449920585</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5302278296126617</v>
+        <v>0.5500105753805141</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5347221667956996</v>
+        <v>0.5496913186102753</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6071459641953532</v>
+        <v>0.5503286349378647</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6087775658267554</v>
+        <v>0.5543047784757085</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5390257480585198</v>
+        <v>0.5406946628249435</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5415758115108029</v>
+        <v>0.5499668771100877</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5415758115108029</v>
+        <v>0.5816030281504657</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5271318370832702</v>
+        <v>0.5553445578692803</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.533697951169677</v>
+        <v>0.5556241070787207</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5344142835479004</v>
+        <v>0.5522413820625584</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5139263793887829</v>
+        <v>0.5522413820625584</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5044941376475565</v>
+        <v>0.5197761610969662</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5019867747882929</v>
+        <v>0.5243922149236577</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4978482093685899</v>
+        <v>0.5243922149236577</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4995201171672347</v>
+        <v>0.5047349769736055</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4975305488822022</v>
+        <v>0.5056103391305041</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4975305488822022</v>
+        <v>0.5031432824384832</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4986449545458174</v>
+        <v>0.5042574885666169</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5090704839134494</v>
+        <v>0.5073614625152645</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5108613148590082</v>
+        <v>0.5073614625152645</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5105827633269748</v>
+        <v>0.5089924655402224</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5118164912084667</v>
+        <v>0.5017497266363905</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5101457806227103</v>
+        <v>0.4975716531913705</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5063252747603578</v>
+        <v>0.4927560638832797</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5007149356298537</v>
+        <v>0.4930346154153131</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5057286636709739</v>
+        <v>0.489412647356953</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5049724241964706</v>
+        <v>0.4778727123257058</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.509508464295121</v>
+        <v>0.475843037408912</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5016699124438307</v>
+        <v>0.4914034128548739</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4995211148446417</v>
+        <v>0.4923984963006122</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5017501257073532</v>
+        <v>0.4912443830761986</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5014709755688757</v>
+        <v>0.4904881436016952</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5013516533509988</v>
+        <v>0.4918809012618623</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5020685843356666</v>
+        <v>0.4994426974004517</v>
       </c>
     </row>
   </sheetData>
